--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0002T0006Z000C1N8_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.74112759326965</v>
+        <v>11.49543323390632</v>
       </c>
       <c r="D2" t="n">
-        <v>56.4379777187807</v>
+        <v>9.171171379301864</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
